--- a/logistic_regression/Supplementary Table 1.xlsx
+++ b/logistic_regression/Supplementary Table 1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gvdovin\ownCloud\Hypoxia Manuscript Final (Figures, Text, Code; Publication Only)\A1 Analysis\logistic_regression\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gvdovin\ownCloud\Hypoxia Manuscript Final (Figures, Text, Code, Publication Only)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81BD538D-7966-4F82-BBA7-9FEA58C195DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB1BFB22-73B4-4BF9-B23B-D8B7D1C1EFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Figure4" sheetId="3" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="137">
   <si>
     <t>Hypoxia Dedifferentiation</t>
   </si>
@@ -202,9 +202,6 @@
     <t xml:space="preserve"> 10%FCS + DMSO    0.1491 0.00451 Inf     0.140    0.1582</t>
   </si>
   <si>
-    <t>Figure 4J</t>
-  </si>
-  <si>
     <t xml:space="preserve">NULL                         25    137.628              </t>
   </si>
   <si>
@@ -353,6 +350,93 @@
   </si>
   <si>
     <t xml:space="preserve"> 10%FCS / (10%FCS + 1%O2)                6.6316 1.8000 Inf    1   6.976 &lt;0.0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NULL                         43    3090.46              </t>
+  </si>
+  <si>
+    <t>Condition  5   2772.3        38     318.19 &lt; 2.2e-16 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Condition     prob      SE  df asymp.LCL asymp.UCL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D3_10uM_LY 0.02574 0.00568 Inf   0.01666    0.0396</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D3_5uM_LY  0.01451 0.00300 Inf   0.00966    0.0217</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D3_DMSO    0.00572 0.00215 Inf   0.00273    0.0119</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D5_10uM_LY 0.44743 0.00785 Inf   0.43211    0.4629</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D5_5uM_LY  0.34037 0.00790 Inf   0.32507    0.3560</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D5_DMSO    0.13397 0.00642 Inf   0.12188    0.1471</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> contrast                odds.ratio      SE  df null z.ratio p.value</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D3_10uM_LY / D3_5uM_LY      1.7943 0.55400 Inf    1   1.892  0.4068</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D3_10uM_LY / D3_DMSO        4.5933 2.03000 Inf    1   3.453  0.0073</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D3_10uM_LY / D5_10uM_LY     0.0326 0.00746 Inf    1 -14.962 &lt;0.0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D3_10uM_LY / D5_5uM_LY      0.0512 0.01170 Inf    1 -12.964 &lt;0.0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D3_10uM_LY / D5_DMSO        0.1708 0.03980 Inf    1  -7.579 &lt;0.0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D3_5uM_LY / D3_DMSO         2.5600 1.11000 Inf    1   2.170  0.2520</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D3_5uM_LY / D5_10uM_LY      0.0182 0.00386 Inf    1 -18.864 &lt;0.0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D3_5uM_LY / D5_5uM_LY       0.0285 0.00608 Inf    1 -16.700 &lt;0.0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D3_5uM_LY / D5_DMSO         0.0952 0.02070 Inf    1 -10.828 &lt;0.0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D3_DMSO / D5_10uM_LY        0.0071 0.00270 Inf    1 -13.010 &lt;0.0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D3_DMSO / D5_5uM_LY         0.0111 0.00424 Inf    1 -11.816 &lt;0.0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D3_DMSO / D5_DMSO           0.0372 0.01420 Inf    1  -8.596 &lt;0.0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D5_10uM_LY / D5_5uM_LY      1.5693 0.07430 Inf    1   9.512 &lt;0.0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D5_10uM_LY / D5_DMSO        5.2343 0.33400 Inf    1  25.944 &lt;0.0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> D5_5uM_LY / D5_DMSO         3.3355 0.21900 Inf    1  18.372 &lt;0.0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P value adjustment: tukey method for comparing a family of 6 estimates </t>
+  </si>
+  <si>
+    <t>Fig. 4J</t>
+  </si>
+  <si>
+    <t>Data Not Shown</t>
+  </si>
+  <si>
+    <t>TGFbeta Inhibition Differentiation Index with 10FCS% Culture</t>
   </si>
 </sst>
 </file>
@@ -701,7 +785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC86C694-4BA1-40D6-A646-2D97E9758148}">
-  <dimension ref="A1:A112"/>
+  <dimension ref="A1:A159"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -756,12 +840,12 @@
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
@@ -801,7 +885,7 @@
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
@@ -819,37 +903,37 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
@@ -920,12 +1004,12 @@
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
@@ -940,244 +1024,243 @@
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>52</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>74</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="2"/>
+      <c r="A61" s="3" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="A62" s="2"/>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>62</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>80</v>
+        <v>121</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>81</v>
+        <v>122</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="2"/>
+      <c r="A71" s="3" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>22</v>
+        <v>124</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="4" t="s">
-        <v>17</v>
+      <c r="A73" s="3" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="4"/>
+      <c r="A74" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="5" t="s">
-        <v>58</v>
+      <c r="A77" s="3" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="5" t="s">
-        <v>51</v>
+      <c r="A78" s="3" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>1</v>
+        <v>131</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="2"/>
+      <c r="A80" s="3" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="A81" s="2"/>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="2"/>
+      <c r="A82" s="3" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="2"/>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="2"/>
+      <c r="A83" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="2"/>
+      <c r="A87" s="5" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="3" t="s">
-        <v>5</v>
+      <c r="A88" s="5" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>82</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" s="3" t="s">
-        <v>83</v>
-      </c>
+      <c r="A90" s="2"/>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A92" s="2"/>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" s="3" t="s">
-        <v>53</v>
-      </c>
+      <c r="A94" s="2"/>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" s="3" t="s">
-        <v>55</v>
-      </c>
+      <c r="A96" s="2"/>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" s="3" t="s">
-        <v>56</v>
-      </c>
+      <c r="A97" s="2"/>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" s="2"/>
+      <c r="A99" s="3" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>62</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
@@ -1185,16 +1268,222 @@
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="2"/>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" s="4" t="s">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" s="4"/>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" s="2"/>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" s="2"/>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="2"/>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="2"/>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" s="2"/>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" s="2"/>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" s="2"/>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1264,12 +1553,12 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1289,22 +1578,22 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
@@ -1322,37 +1611,37 @@
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
@@ -1488,7 +1777,7 @@
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
@@ -1508,7 +1797,7 @@
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
@@ -1531,7 +1820,7 @@
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
@@ -1644,7 +1933,7 @@
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
@@ -1654,7 +1943,7 @@
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
@@ -1664,7 +1953,7 @@
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
